--- a/lab_01/dataset.xlsx
+++ b/lab_01/dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BMSTU\BMSTU-9-sem-AI-System\lab_01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35AFEEAD-0DB4-40A5-92C9-CBFF97DD0259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91FB19E0-9F93-43B1-B84A-E6C92F52426C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="28080" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="162">
   <si>
     <t>верхние ноты</t>
   </si>
@@ -528,6 +528,12 @@
   </si>
   <si>
     <t>Белый кедр;Пачули</t>
+  </si>
+  <si>
+    <t>Шлейд - способность духов пахнуть на расстоянии</t>
+  </si>
+  <si>
+    <t>аромат</t>
   </si>
 </sst>
 </file>
@@ -598,25 +604,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -628,6 +627,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -635,312 +635,152 @@
   <dxfs count="33">
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
         <color theme="1"/>
         <name val="Times New Roman"/>
         <family val="1"/>
         <charset val="204"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
         <color theme="1"/>
         <name val="Times New Roman"/>
         <family val="1"/>
         <charset val="204"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
         <color theme="1"/>
         <name val="Times New Roman"/>
         <family val="1"/>
         <charset val="204"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
         <color theme="1"/>
         <name val="Times New Roman"/>
         <family val="1"/>
         <charset val="204"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
         <color theme="1"/>
         <name val="Times New Roman"/>
         <family val="1"/>
         <charset val="204"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
         <name val="Times New Roman"/>
         <family val="1"/>
         <charset val="204"/>
@@ -971,125 +811,7 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
+        <color theme="1"/>
         <name val="Times New Roman"/>
         <family val="1"/>
         <charset val="204"/>
@@ -1120,6 +842,7 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
+        <color theme="1"/>
         <name val="Times New Roman"/>
         <family val="1"/>
         <charset val="204"/>
@@ -1150,6 +873,191 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
         <name val="Times New Roman"/>
         <family val="1"/>
         <charset val="204"/>
@@ -1180,64 +1088,7 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
+        <color theme="1"/>
         <name val="Times New Roman"/>
         <family val="1"/>
         <charset val="204"/>
@@ -1262,138 +1113,303 @@
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-        <scheme val="none"/>
-      </font>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1473,24 +1489,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DE7B189E-9B4D-45DB-8D9B-A2839747DF00}" name="data" displayName="data" ref="A1:O26" tableType="queryTable" totalsRowCount="1" headerRowDxfId="32" dataDxfId="30" totalsRowDxfId="31">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DE7B189E-9B4D-45DB-8D9B-A2839747DF00}" name="data" displayName="data" ref="A1:O26" tableType="queryTable" totalsRowCount="1" headerRowDxfId="32" dataDxfId="0" totalsRowDxfId="31">
   <autoFilter ref="A1:O25" xr:uid="{DE7B189E-9B4D-45DB-8D9B-A2839747DF00}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{809AAFB5-7E25-4C9A-AA55-7D3589FCA4D8}" uniqueName="1" name="Название" queryTableFieldId="1" dataDxfId="29" totalsRowDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{3513B5D4-4D35-4010-BE6F-A8BDC2629894}" uniqueName="2" name="Пол" queryTableFieldId="2" dataDxfId="15" totalsRowDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{B844D835-DCEC-4BCC-AF93-A22494C8F881}" uniqueName="3" name="Бренд" queryTableFieldId="3" dataDxfId="28" totalsRowDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{ACED0A68-CDEC-4364-B215-2DDFD1FC4E42}" uniqueName="4" name="Страна" queryTableFieldId="4" dataDxfId="27" totalsRowDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{5DFF9EC6-48DD-4107-A2E3-B3EEF498F121}" uniqueName="6" name="Концентрация" queryTableFieldId="6" dataDxfId="26" totalsRowDxfId="10"/>
-    <tableColumn id="11" xr3:uid="{C59CB4A3-C323-4CD2-92F6-05422BF98FE0}" uniqueName="11" name="Семейства" queryTableFieldId="11" dataDxfId="25" totalsRowDxfId="9"/>
-    <tableColumn id="12" xr3:uid="{FDD934CA-CEEB-49C2-A788-393F08B24FEB}" uniqueName="12" name="Стойкость минимум (ч)" queryTableFieldId="12" dataDxfId="24" totalsRowDxfId="8"/>
-    <tableColumn id="13" xr3:uid="{54EF7822-C8A5-4C18-8F94-0876CFEA12F5}" uniqueName="13" name="Стойкость максимум (ч)" queryTableFieldId="13" dataDxfId="23" totalsRowDxfId="7"/>
-    <tableColumn id="14" xr3:uid="{B7F29644-78CB-48DB-BC54-E1D651089D53}" uniqueName="14" name="Шлейф" queryTableFieldId="14" dataDxfId="22" totalsRowDxfId="6"/>
-    <tableColumn id="16" xr3:uid="{2588891B-547B-4FE0-885A-2B31D0A26194}" uniqueName="16" name="Возраст (до 18)" queryTableFieldId="16" dataDxfId="21" totalsRowDxfId="5"/>
-    <tableColumn id="21" xr3:uid="{3E505097-646A-4D83-94BE-08C635410F41}" uniqueName="21" name="мл" queryTableFieldId="21" dataDxfId="20" totalsRowDxfId="4"/>
-    <tableColumn id="22" xr3:uid="{E3504C51-CAFD-4785-9987-605193AB9563}" uniqueName="22" name="Цена" queryTableFieldId="22" dataDxfId="19" totalsRowDxfId="3"/>
-    <tableColumn id="24" xr3:uid="{2E471924-75DB-4C06-8D75-3626984C094F}" uniqueName="24" name="верхние ноты" queryTableFieldId="24" dataDxfId="18" totalsRowDxfId="2"/>
-    <tableColumn id="25" xr3:uid="{DAADFF7E-0C79-4A16-9191-3A27BB801717}" uniqueName="25" name="ноты сердца" queryTableFieldId="25" dataDxfId="17" totalsRowDxfId="1"/>
-    <tableColumn id="26" xr3:uid="{A09FF61A-888E-46B3-9C66-1C296EFE60AF}" uniqueName="26" name="базовые ноты" queryTableFieldId="26" dataDxfId="16" totalsRowDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{809AAFB5-7E25-4C9A-AA55-7D3589FCA4D8}" uniqueName="1" name="Название" queryTableFieldId="1" dataDxfId="15" totalsRowDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{3513B5D4-4D35-4010-BE6F-A8BDC2629894}" uniqueName="2" name="Пол" queryTableFieldId="2" dataDxfId="14" totalsRowDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{B844D835-DCEC-4BCC-AF93-A22494C8F881}" uniqueName="3" name="Бренд" queryTableFieldId="3" dataDxfId="13" totalsRowDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{ACED0A68-CDEC-4364-B215-2DDFD1FC4E42}" uniqueName="4" name="Страна" queryTableFieldId="4" dataDxfId="12" totalsRowDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{5DFF9EC6-48DD-4107-A2E3-B3EEF498F121}" uniqueName="6" name="Концентрация" queryTableFieldId="6" dataDxfId="11" totalsRowDxfId="26"/>
+    <tableColumn id="11" xr3:uid="{C59CB4A3-C323-4CD2-92F6-05422BF98FE0}" uniqueName="11" name="Семейства" queryTableFieldId="11" dataDxfId="10" totalsRowDxfId="25"/>
+    <tableColumn id="12" xr3:uid="{FDD934CA-CEEB-49C2-A788-393F08B24FEB}" uniqueName="12" name="Стойкость минимум (ч)" queryTableFieldId="12" dataDxfId="9" totalsRowDxfId="24"/>
+    <tableColumn id="13" xr3:uid="{54EF7822-C8A5-4C18-8F94-0876CFEA12F5}" uniqueName="13" name="Стойкость максимум (ч)" queryTableFieldId="13" dataDxfId="8" totalsRowDxfId="23"/>
+    <tableColumn id="14" xr3:uid="{B7F29644-78CB-48DB-BC54-E1D651089D53}" uniqueName="14" name="Шлейф" queryTableFieldId="14" dataDxfId="7" totalsRowDxfId="22"/>
+    <tableColumn id="16" xr3:uid="{2588891B-547B-4FE0-885A-2B31D0A26194}" uniqueName="16" name="Возраст (до 18)" queryTableFieldId="16" dataDxfId="6" totalsRowDxfId="21"/>
+    <tableColumn id="21" xr3:uid="{3E505097-646A-4D83-94BE-08C635410F41}" uniqueName="21" name="мл" queryTableFieldId="21" dataDxfId="5" totalsRowDxfId="20"/>
+    <tableColumn id="22" xr3:uid="{E3504C51-CAFD-4785-9987-605193AB9563}" uniqueName="22" name="Цена" queryTableFieldId="22" dataDxfId="4" totalsRowDxfId="19"/>
+    <tableColumn id="24" xr3:uid="{2E471924-75DB-4C06-8D75-3626984C094F}" uniqueName="24" name="верхние ноты" queryTableFieldId="24" dataDxfId="3" totalsRowDxfId="18"/>
+    <tableColumn id="25" xr3:uid="{DAADFF7E-0C79-4A16-9191-3A27BB801717}" uniqueName="25" name="ноты сердца" queryTableFieldId="25" dataDxfId="2" totalsRowDxfId="17"/>
+    <tableColumn id="26" xr3:uid="{A09FF61A-888E-46B3-9C66-1C296EFE60AF}" uniqueName="26" name="базовые ноты" queryTableFieldId="26" dataDxfId="1" totalsRowDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1759,1199 +1775,1209 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{137739D4-0466-493E-9285-A38B1B0FDE11}">
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5703125" style="10" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="48.140625" style="10" customWidth="1"/>
-    <col min="7" max="7" width="25.140625" style="10" customWidth="1"/>
-    <col min="8" max="8" width="24" style="10" customWidth="1"/>
-    <col min="9" max="9" width="16.7109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.7109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="66.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="51.7109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="59.140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="57.7109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="10"/>
+    <col min="1" max="1" width="37.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5703125" style="7" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="48.140625" style="7" customWidth="1"/>
+    <col min="7" max="7" width="25.140625" style="7" customWidth="1"/>
+    <col min="8" max="8" width="24" style="7" customWidth="1"/>
+    <col min="9" max="9" width="16.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="66.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="51.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="59.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="57.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="O1" s="6" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="2">
         <v>2</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2" s="2">
         <v>5</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="2">
         <v>10234</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="N2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="O2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="2">
         <v>12</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="2">
         <v>1000</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="4">
+      <c r="L3" s="2">
         <v>5170</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="O3" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="2">
         <v>5</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="2">
         <v>12</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5">
+      <c r="J4" s="2"/>
+      <c r="K4" s="2">
         <v>100</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4" s="2">
         <v>12268</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="M4" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="N4" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="O4" s="7" t="s">
+      <c r="O4" s="4" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="2">
         <v>5</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="2">
         <v>12</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5">
+      <c r="J5" s="2"/>
+      <c r="K5" s="2">
         <v>100</v>
       </c>
-      <c r="L5" s="4">
+      <c r="L5" s="2">
         <v>9197</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="M5" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="N5" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="O5" s="8" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="2">
         <v>2</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="2">
         <v>5</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K6" s="5">
+      <c r="K6" s="2">
         <v>8</v>
       </c>
-      <c r="L6" s="4">
+      <c r="L6" s="2">
         <v>1859</v>
       </c>
-      <c r="M6" s="6" t="s">
+      <c r="M6" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="N6" s="6" t="s">
+      <c r="N6" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="O6" s="6" t="s">
+      <c r="O6" s="3" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="2">
         <v>5</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7" s="2">
         <v>12</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K7" s="2">
         <v>60</v>
       </c>
-      <c r="L7" s="4">
+      <c r="L7" s="2">
         <v>11388</v>
       </c>
-      <c r="M7" s="6" t="s">
+      <c r="M7" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="N7" s="6" t="s">
+      <c r="N7" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="O7" s="6" t="s">
+      <c r="O7" s="3" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="2">
         <v>5</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="2">
         <v>12</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5">
+      <c r="J8" s="2"/>
+      <c r="K8" s="2">
         <v>125</v>
       </c>
-      <c r="L8" s="4">
+      <c r="L8" s="2">
         <v>37063</v>
       </c>
-      <c r="M8" s="6" t="s">
+      <c r="M8" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="N8" s="6" t="s">
+      <c r="N8" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="O8" s="6" t="s">
+      <c r="O8" s="3" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="2">
         <v>2</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="2">
         <v>5</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="J9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K9" s="5">
+      <c r="K9" s="2">
         <v>100</v>
       </c>
-      <c r="L9" s="4">
+      <c r="L9" s="2">
         <v>5843</v>
       </c>
-      <c r="M9" s="6" t="s">
+      <c r="M9" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="N9" s="6" t="s">
+      <c r="N9" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="O9" s="6" t="s">
+      <c r="O9" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10" s="2">
         <v>2</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10" s="2">
         <v>5</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="J10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="K10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="L10" s="4">
+      <c r="L10" s="2">
         <v>10497</v>
       </c>
-      <c r="M10" s="6" t="s">
+      <c r="M10" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="N10" s="6" t="s">
+      <c r="N10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="O10" s="6" t="s">
+      <c r="O10" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G11" s="2">
         <v>2</v>
       </c>
-      <c r="H11" s="4">
+      <c r="H11" s="2">
         <v>5</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="J11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="K11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="L11" s="4">
+      <c r="L11" s="2">
         <v>5774</v>
       </c>
-      <c r="M11" s="6" t="s">
+      <c r="M11" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="N11" s="6" t="s">
+      <c r="N11" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="O11" s="6" t="s">
+      <c r="O11" s="3" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G12" s="2">
         <v>12</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H12" s="2">
         <v>1000</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="J12" s="5" t="s">
+      <c r="J12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K12" s="5" t="s">
+      <c r="K12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="L12" s="4">
+      <c r="L12" s="2">
         <v>8805</v>
       </c>
-      <c r="M12" s="6" t="s">
+      <c r="M12" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="N12" s="6" t="s">
+      <c r="N12" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="O12" s="6" t="s">
+      <c r="O12" s="3" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G13" s="2">
         <v>12</v>
       </c>
-      <c r="H13" s="4">
+      <c r="H13" s="2">
         <v>1000</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J13" s="5" t="s">
+      <c r="J13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="K13" s="5">
+      <c r="K13" s="2">
         <v>50</v>
       </c>
-      <c r="L13" s="4">
+      <c r="L13" s="2">
         <v>11586</v>
       </c>
-      <c r="M13" s="6" t="s">
+      <c r="M13" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="N13" s="6" t="s">
+      <c r="N13" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="O13" s="6" t="s">
+      <c r="O13" s="3" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G14" s="2">
         <v>5</v>
       </c>
-      <c r="H14" s="4">
+      <c r="H14" s="2">
         <v>12</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="I14" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="J14" s="5" t="s">
+      <c r="J14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K14" s="5">
+      <c r="K14" s="2">
         <v>100</v>
       </c>
-      <c r="L14" s="4">
+      <c r="L14" s="2">
         <v>19032</v>
       </c>
-      <c r="M14" s="6" t="s">
+      <c r="M14" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="N14" s="6" t="s">
+      <c r="N14" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="O14" s="6" t="s">
+      <c r="O14" s="3" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G15" s="4">
+      <c r="G15" s="2">
         <v>2</v>
       </c>
-      <c r="H15" s="4">
+      <c r="H15" s="2">
         <v>5</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="I15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5">
+      <c r="J15" s="2"/>
+      <c r="K15" s="2">
         <v>125</v>
       </c>
-      <c r="L15" s="4">
+      <c r="L15" s="2">
         <v>29303</v>
       </c>
-      <c r="M15" s="6" t="s">
+      <c r="M15" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="N15" s="6" t="s">
+      <c r="N15" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="O15" s="6" t="s">
+      <c r="O15" s="3" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G16" s="4">
+      <c r="G16" s="2">
         <v>12</v>
       </c>
-      <c r="H16" s="4">
+      <c r="H16" s="2">
         <v>1000</v>
       </c>
-      <c r="I16" s="5" t="s">
+      <c r="I16" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J16" s="5" t="s">
+      <c r="J16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K16" s="5" t="s">
+      <c r="K16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="L16" s="4">
+      <c r="L16" s="2">
         <v>3179</v>
       </c>
-      <c r="M16" s="6" t="s">
+      <c r="M16" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="N16" s="6" t="s">
+      <c r="N16" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="O16" s="6" t="s">
+      <c r="O16" s="3" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G17" s="2">
         <v>2</v>
       </c>
-      <c r="H17" s="4">
+      <c r="H17" s="2">
         <v>5</v>
       </c>
-      <c r="I17" s="5" t="s">
+      <c r="I17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J17" s="5" t="s">
+      <c r="J17" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K17" s="5" t="s">
+      <c r="K17" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="L17" s="4">
+      <c r="L17" s="2">
         <v>7887</v>
       </c>
-      <c r="M17" s="6" t="s">
+      <c r="M17" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="N17" s="6" t="s">
+      <c r="N17" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="O17" s="6" t="s">
+      <c r="O17" s="3" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="G18" s="4">
+      <c r="G18" s="2">
         <v>2</v>
       </c>
-      <c r="H18" s="4">
+      <c r="H18" s="2">
         <v>5</v>
       </c>
-      <c r="I18" s="5" t="s">
+      <c r="I18" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J18" s="5" t="s">
+      <c r="J18" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K18" s="5">
+      <c r="K18" s="2">
         <v>100</v>
       </c>
-      <c r="L18" s="4">
+      <c r="L18" s="2">
         <v>22557</v>
       </c>
-      <c r="M18" s="6" t="s">
+      <c r="M18" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="N18" s="6" t="s">
+      <c r="N18" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="O18" s="6" t="s">
+      <c r="O18" s="3" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G19" s="4">
+      <c r="G19" s="2">
         <v>5</v>
       </c>
-      <c r="H19" s="4">
+      <c r="H19" s="2">
         <v>12</v>
       </c>
-      <c r="I19" s="5" t="s">
+      <c r="I19" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5">
+      <c r="J19" s="2"/>
+      <c r="K19" s="2">
         <v>90</v>
       </c>
-      <c r="L19" s="4">
+      <c r="L19" s="2">
         <v>5927</v>
       </c>
-      <c r="M19" s="6" t="s">
+      <c r="M19" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="N19" s="6" t="s">
+      <c r="N19" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="O19" s="6" t="s">
+      <c r="O19" s="3" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="G20" s="4">
+      <c r="G20" s="2">
         <v>12</v>
       </c>
-      <c r="H20" s="4">
+      <c r="H20" s="2">
         <v>1000</v>
       </c>
-      <c r="I20" s="5" t="s">
+      <c r="I20" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J20" s="5" t="s">
+      <c r="J20" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K20" s="5">
+      <c r="K20" s="2">
         <v>30</v>
       </c>
-      <c r="L20" s="4">
+      <c r="L20" s="2">
         <v>4703</v>
       </c>
-      <c r="M20" s="6" t="s">
+      <c r="M20" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="N20" s="6" t="s">
+      <c r="N20" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="O20" s="6" t="s">
+      <c r="O20" s="3" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="G21" s="4">
+      <c r="G21" s="2">
         <v>12</v>
       </c>
-      <c r="H21" s="4">
+      <c r="H21" s="2">
         <v>1000</v>
       </c>
-      <c r="I21" s="5" t="s">
+      <c r="I21" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J21" s="5" t="s">
+      <c r="J21" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K21" s="5" t="s">
+      <c r="K21" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="L21" s="4">
+      <c r="L21" s="2">
         <v>13047</v>
       </c>
-      <c r="M21" s="6" t="s">
+      <c r="M21" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="N21" s="6" t="s">
+      <c r="N21" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="O21" s="6" t="s">
+      <c r="O21" s="3" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F22" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G22" s="4">
+      <c r="G22" s="2">
         <v>2</v>
       </c>
-      <c r="H22" s="4">
+      <c r="H22" s="2">
         <v>5</v>
       </c>
-      <c r="I22" s="5" t="s">
+      <c r="I22" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J22" s="5" t="s">
+      <c r="J22" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="K22" s="5">
+      <c r="K22" s="2">
         <v>30</v>
       </c>
-      <c r="L22" s="4">
+      <c r="L22" s="2">
         <v>5582</v>
       </c>
-      <c r="M22" s="6" t="s">
+      <c r="M22" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="N22" s="6" t="s">
+      <c r="N22" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="O22" s="6" t="s">
+      <c r="O22" s="3" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F23" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G23" s="4">
+      <c r="G23" s="2">
         <v>12</v>
       </c>
-      <c r="H23" s="4">
+      <c r="H23" s="2">
         <v>1000</v>
       </c>
-      <c r="I23" s="5" t="s">
+      <c r="I23" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J23" s="5" t="s">
+      <c r="J23" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K23" s="5">
+      <c r="K23" s="2">
         <v>100</v>
       </c>
-      <c r="L23" s="4">
+      <c r="L23" s="2">
         <v>51916</v>
       </c>
-      <c r="M23" s="6" t="s">
+      <c r="M23" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="N23" s="6" t="s">
+      <c r="N23" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="O23" s="6" t="s">
+      <c r="O23" s="3" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G24" s="4">
+      <c r="G24" s="2">
         <v>5</v>
       </c>
-      <c r="H24" s="4">
+      <c r="H24" s="2">
         <v>12</v>
       </c>
-      <c r="I24" s="5" t="s">
+      <c r="I24" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J24" s="5" t="s">
+      <c r="J24" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K24" s="5">
+      <c r="K24" s="2">
         <v>100</v>
       </c>
-      <c r="L24" s="4">
+      <c r="L24" s="2">
         <v>13909</v>
       </c>
-      <c r="M24" s="6" t="s">
+      <c r="M24" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="N24" s="6" t="s">
+      <c r="N24" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="O24" s="6" t="s">
+      <c r="O24" s="3" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="25" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G25" s="4">
+      <c r="G25" s="2">
         <v>2</v>
       </c>
-      <c r="H25" s="4">
+      <c r="H25" s="2">
         <v>5</v>
       </c>
-      <c r="I25" s="5" t="s">
+      <c r="I25" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J25" s="5" t="s">
+      <c r="J25" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K25" s="5">
+      <c r="K25" s="2">
         <v>50</v>
       </c>
-      <c r="L25" s="4">
+      <c r="L25" s="2">
         <v>13412</v>
       </c>
-      <c r="M25" s="6" t="s">
+      <c r="M25" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="N25" s="6" t="s">
+      <c r="N25" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="O25" s="6" t="s">
+      <c r="O25" s="3" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>161</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
